--- a/data/seed/portfolio/L-2025-7064/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2025-7064/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -542,35 +542,35 @@
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>32864000</v>
+        <v>8875000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5196</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6359 01.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>180664000</v>
+        <v>156675000</v>
       </c>
     </row>
     <row r="9">
@@ -582,35 +582,35 @@
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>24970000</v>
+        <v>5796000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>224085958</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000638419757001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Shartnoma №190/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по дог. №118/26 от 01.07.2026</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>205634000</v>
+        <v>162471000</v>
       </c>
     </row>
     <row r="10">
@@ -620,312 +620,317 @@
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n">
-        <v>15310000</v>
-      </c>
-      <c r="D10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>30166000</v>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ilhom Logistik MChJ</t>
+          <t>Navoiy Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>248917833</t>
+          <t>369710937</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000947306345001</t>
+          <t>20208000695033896001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №195/26, QQS BILAN</t>
+          <t>Предоплата за товар по договору №167/26 от 02.07.2026</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>190324000</v>
+        <v>192637000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46206</v>
+        <v>46205</v>
       </c>
       <c r="B11" t="n">
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n"/>
       <c r="D11" s="2" t="n">
-        <v>10322000</v>
+        <v>6142000</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9371 03.07.2026, QQS bilan</t>
+          <t>Оплата по с/ф №6708 за поставленный товар</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>200646000</v>
+        <v>198779000</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B12" t="n">
         <v>104</v>
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>41467000</v>
+        <v>209392000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Andijon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>265350564</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000730811872001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5390</t>
+          <t>Shartnoma №160/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>242113000</v>
+        <v>408171000</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B13" t="n">
         <v>105</v>
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>16048000</v>
+        <v>14606000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №25/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №23/26 от 03.07.2026</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>258161000</v>
+        <v>422777000</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B14" t="n">
         <v>106</v>
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>15852000</v>
+        <v>9502000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9514 06.07.2026, QQS bilan</t>
+          <t>Оплата по с/ф №5989 за поставленный товар</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>274013000</v>
+        <v>432279000</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B15" t="n">
         <v>107</v>
       </c>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n">
-        <v>14354000</v>
-      </c>
+      <c r="C15" s="2" t="n">
+        <v>9808000</v>
+      </c>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Denov Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>309642814</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000113550674001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №50/26 от 06.07.2026</t>
+          <t>Предоплата за материалы по договору №37/26</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>288367000</v>
+        <v>422471000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B16" t="n">
         <v>108</v>
       </c>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n">
-        <v>13925000</v>
-      </c>
+      <c r="C16" s="2" t="n">
+        <v>13228000</v>
+      </c>
+      <c r="D16" s="2" t="n"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>209058766</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000571672220001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №3720</t>
+          <t>Materiallar uchun oldindan to'lov, shartn. №81/26</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>302292000</v>
+        <v>409243000</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B17" t="n">
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>28416000</v>
+        <v>26759000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Toshkent Farm Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>209058766</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000571672220001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>ISH HAQI TO'LOVI IYUN 2026 (PLASTIK KARTALARGA)</t>
+          <t>Оплата за упаковочные материалы, с/ф №2145</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>273876000</v>
+        <v>382484000</v>
       </c>
     </row>
     <row r="18">
@@ -936,22 +941,22 @@
         <v>110</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>29240000</v>
+        <v>8478000</v>
       </c>
       <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>209058766</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000571672220001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -961,37 +966,37 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №7407</t>
+          <t>Оплата за упаковочные материалы, с/ф №6838</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>244636000</v>
+        <v>374006000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
-        <v>42647000</v>
-      </c>
+      <c r="C19" s="2" t="n">
+        <v>9689000</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Saodat Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>343642020</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000791511261001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1001,432 +1006,427 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Shartnoma №13/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за сырье по дог. №179/26 от 06.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>287283000</v>
+        <v>364317000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>29254000</v>
+        <v>19383000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ilhom Logistik MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>248917833</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000947306345001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №147/26</t>
+          <t>ОПЛАТА ЗА ТРАНСПОРТНЫЕ УСЛУГИ ПО ДОГОВОРУ №109/26</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>258029000</v>
+        <v>344934000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>3991000</v>
+        <v>28416000</v>
       </c>
       <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish MChJ</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>372974759</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000631506069001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Bino ijarasi uchun to'lov iyul</t>
+          <t>ЗАРАБОТНАЯ ПЛАТА ЗА ИЮНЬ 2026 Г. (ПЕРЕЧИСЛЕНИЕ НА ПЛАСТИКОВЫЕ КАРТЫ)</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>254038000</v>
+        <v>316518000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46217</v>
+        <v>46211</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
       <c r="C22" s="2" t="n"/>
       <c r="D22" s="2" t="n">
-        <v>18786000</v>
+        <v>7835000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №4608</t>
+          <t>Оплата за продукцию по договору №23/26, НДС 12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>272824000</v>
+        <v>324353000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46217</v>
+        <v>46211</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n">
-        <v>9830000</v>
-      </c>
+      <c r="C23" s="2" t="n">
+        <v>8594000</v>
+      </c>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>209058766</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000571672220001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Shartnoma №254/26 bo'yicha oldindan to'lov</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTNOMA №207/26</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>282654000</v>
+        <v>315759000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46217</v>
+        <v>46212</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>3875000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>30437000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>367631266</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000979177978001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Iyun oyi uchun ijtimoiy soliq</t>
+          <t>Оплата за продукцию по договору №128/26, НДС 12%</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>278779000</v>
+        <v>346196000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46217</v>
+        <v>46212</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>3875000</v>
+        <v>3991000</v>
       </c>
       <c r="D25" s="2" t="n"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Shodlik Qurilish MChJ</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>353396700</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000029513757001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Ijara haqi iyul oyi uchun, shartnoma №12/23</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>274904000</v>
+        <v>342205000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
-      <c r="C26" s="2" t="n">
-        <v>16307000</v>
-      </c>
-      <c r="D26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n">
+        <v>18020000</v>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №70/26</t>
+          <t>Предоплата за товар по договору №69/26 от 13.07.2026</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>258597000</v>
+        <v>360225000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46218</v>
+        <v>46216</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
-      <c r="C27" s="2" t="n">
-        <v>27600000</v>
-      </c>
-      <c r="D27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n">
+        <v>15379000</v>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-7064)</t>
+          <t>Navoiy Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>16307000208536163417</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-7064 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Оплата за продукцию по договору №293/26, НДС 12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>230997000</v>
+        <v>375604000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n">
-        <v>96648000</v>
-      </c>
+      <c r="C28" s="2" t="n">
+        <v>3875000</v>
+      </c>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Shartnoma №25/26 bo'yicha oldindan to'lov</t>
+          <t>Уплата социального налога за июнь</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>327645000</v>
+        <v>371729000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46220</v>
+        <v>46218</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n">
-        <v>22095000</v>
-      </c>
+      <c r="C29" s="2" t="n">
+        <v>3875000</v>
+      </c>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №8583 17.07.2026, QQS bilan</t>
+          <t>Налог на доходы физических лиц за июнь 2026 г.</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>349740000</v>
+        <v>367854000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46220</v>
+        <v>46218</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>37735000</v>
+        <v>27600000</v>
       </c>
       <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Durdona Avto Ehtiyot MChJ</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>243368843</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-7064)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000420339260001</t>
+          <t>16307000208536163417</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1436,11 +1436,11 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tovrlar uchun to'lov h/f №1703</t>
+          <t>Kredit shartnomasi L-2025-7064 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>312005000</v>
+        <v>340254000</v>
       </c>
     </row>
     <row r="31">
@@ -1452,35 +1452,35 @@
       </c>
       <c r="C31" s="2" t="n"/>
       <c r="D31" s="2" t="n">
-        <v>100006000</v>
+        <v>57232000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Navoiy Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>369710937</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000695033896001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6216</t>
+          <t>Оплата по с/ф №2644 за поставленный товар</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>412011000</v>
+        <v>397486000</v>
       </c>
     </row>
     <row r="32">
@@ -1492,115 +1492,115 @@
       </c>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n">
-        <v>26308000</v>
+        <v>12349000</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №802 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №65/26 от 20.07.2026</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>438319000</v>
+        <v>409835000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
       <c r="C33" s="2" t="n"/>
       <c r="D33" s="2" t="n">
-        <v>15401000</v>
+        <v>10631000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Nukus Savdo AJ</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>237734747</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000287266283001</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №7202 21.07.2026, QQS BILAN</t>
+          <t>Mahsulot uchun to'lov, shartnoma №213/26, QQS 12%</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>453720000</v>
+        <v>420466000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46224</v>
+        <v>46223</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>6675000</v>
+        <v>74182000</v>
       </c>
       <c r="D34" s="2" t="n"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
+          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №9214</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>447045000</v>
+        <v>346284000</v>
       </c>
     </row>
     <row r="35">
@@ -1610,23 +1610,23 @@
       <c r="B35" t="n">
         <v>127</v>
       </c>
-      <c r="C35" s="2" t="n">
-        <v>13033000</v>
-      </c>
-      <c r="D35" s="2" t="n"/>
+      <c r="C35" s="2" t="n"/>
+      <c r="D35" s="2" t="n">
+        <v>5357000</v>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ilhom Logistik MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>248917833</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000947306345001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1636,392 +1636,397 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №34/26</t>
+          <t>Оплата по счет-фактуре №2105 за поставленный товар</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>434012000</v>
+        <v>351641000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46226</v>
+        <v>46225</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>7717000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>6325000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Shartnoma №296/26 bo'yicha oldindan to'lov</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №207/26, QQS bilan</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>441729000</v>
+        <v>345316000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46230</v>
+        <v>46225</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>2494000</v>
+        <v>6633000</v>
       </c>
       <c r="D37" s="2" t="n"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000025679860001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>НДСза июнь 2026 г.</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>439235000</v>
+        <v>338683000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46230</v>
+        <v>46226</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>39889000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>17007000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ilhom Logistik MChJ</t>
+          <t>Navoiy Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>248917833</t>
+          <t>369710937</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>20208000947306345001</t>
+          <t>20208000695033896001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5872</t>
+          <t>Предоплата за товар по договору №93/26 от 23.07.2026</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>399346000</v>
+        <v>355690000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46230</v>
+        <v>46227</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46709000</v>
+        <v>9786000</v>
       </c>
       <c r="D39" s="2" t="n"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ilhom Mebel AJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>298850397</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>20208000121172763001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №256/26, QQS bilan</t>
+          <t>Предоплата за материалы по договору №175/26</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>352637000</v>
+        <v>345904000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46233</v>
+        <v>46227</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>47000000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>14039000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Navoiy Metall AJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>295096428</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000411135506001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №270/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №444</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>399637000</v>
+        <v>331865000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n">
+        <v>28247000</v>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>367631266</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000979177978001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Bank xizmati uchun komissiya</t>
+          <t>Оплата за продукцию по дог. №1/26, НДС 12%</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>399337000</v>
+        <v>360112000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>252764000</v>
+        <v>2494000</v>
       </c>
       <c r="D42" s="2" t="n"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000179412176001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №287/26</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>146573000</v>
+        <v>357618000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
-      <c r="C43" s="2" t="n"/>
-      <c r="D43" s="2" t="n">
-        <v>22916000</v>
-      </c>
+      <c r="C43" s="2" t="n">
+        <v>10327000</v>
+      </c>
+      <c r="D43" s="2" t="n"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Denov Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>309642814</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000113550674001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №284/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №2165</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>169489000</v>
+        <v>347291000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n">
-        <v>8474000</v>
-      </c>
+      <c r="C44" s="2" t="n">
+        <v>7944000</v>
+      </c>
+      <c r="D44" s="2" t="n"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Denov Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>309642814</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000113550674001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>SHARTNOMA №40/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за транспортные услуги по договору №81/26</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>177963000</v>
+        <v>339347000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>3560000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>24707000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2031,197 +2036,192 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9797 03.08.2026, QQS bilan</t>
+          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №183/26 ОТ 28.07.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>181523000</v>
+        <v>314640000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n">
-        <v>17432000</v>
-      </c>
+      <c r="C46" s="2" t="n">
+        <v>14483000</v>
+      </c>
+      <c r="D46" s="2" t="n"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>209058766</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000571672220001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №281/26 от 04.08.2026</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №119/26</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>198955000</v>
+        <v>300157000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>48736000</v>
+        <v>42702000</v>
       </c>
       <c r="D47" s="2" t="n"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №53/26</t>
+          <t>Предоплата за материалы по договору №81/26</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>150219000</v>
+        <v>257455000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46239</v>
+        <v>46234</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>14332000</v>
+        <v>65742000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №190/26 от 05.08.2026</t>
+          <t>Оплата по счет-фактуре №2476 за поставленный товар</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>164551000</v>
+        <v>323197000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46240</v>
+        <v>46234</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
-      <c r="C49" s="2" t="n"/>
-      <c r="D49" s="2" t="n">
-        <v>5679000</v>
-      </c>
+      <c r="C49" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D49" s="2" t="n"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>222000978</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7148</t>
+          <t>Комиссия банка за расчетно-кассовое обслуживание за июль</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>170230000</v>
+        <v>322897000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46240</v>
+        <v>46234</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>7000000</v>
+        <v>177115000</v>
       </c>
       <c r="D50" s="2" t="n"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>209058766</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000571672220001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2231,152 +2231,157 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9664</t>
+          <t>Оплата за упковочные материалы, с/ф №643</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>163230000</v>
+        <v>145782000</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>28111000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>40283000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Navoiy Metall Servis MChJ</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>ISH HAQI TO'LOVI IYUL 2026 (PLASTIK KARTALARGA)</t>
+          <t>Оплата за продукцию по договору №174/26, НДС 12%</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>135119000</v>
+        <v>186065000</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46241</v>
+        <v>46237</v>
       </c>
       <c r="B52" t="n">
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n"/>
       <c r="D52" s="2" t="n">
-        <v>7458000</v>
+        <v>6131000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Nukus Savdo AJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>237734747</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000287266283001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №2546 07.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по дог. №98/26 от 03.08.2026</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>142577000</v>
+        <v>192196000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n">
-        <v>25264000</v>
-      </c>
+      <c r="C53" s="2" t="n">
+        <v>36640000</v>
+      </c>
+      <c r="D53" s="2" t="n"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon MChJ</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>224085958</t>
+          <t>209058766</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000638419757001</t>
+          <t>20208000571672220001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №5768 от 10.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товары согласно с/ф №516</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>167841000</v>
+        <v>155556000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46244</v>
+        <v>46239</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>25241000</v>
+        <v>8874000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2386,277 +2391,272 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Shartnoma №41/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №8930 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>193082000</v>
+        <v>164430000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46244</v>
+        <v>46239</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n">
-        <v>3916000</v>
-      </c>
+      <c r="C55" s="2" t="n">
+        <v>28111000</v>
+      </c>
+      <c r="D55" s="2" t="n"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>222000978</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2791 10.08.2026, QQS bilan</t>
+          <t>Iyul oyi uchun ish haqi, reestr №647</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>196998000</v>
+        <v>136319000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n"/>
       <c r="D56" s="2" t="n">
-        <v>3830000</v>
+        <v>48647000</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Nukus Savdo AJ</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>237734747</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000287266283001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9897 10.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по договору №125/26, НДС 12%</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>200828000</v>
+        <v>184966000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
-      <c r="C57" s="2" t="n">
-        <v>3948000</v>
-      </c>
-      <c r="D57" s="2" t="n"/>
+      <c r="C57" s="2" t="n"/>
+      <c r="D57" s="2" t="n">
+        <v>14717000</v>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>372974759</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000631506069001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №53/25</t>
+          <t>Оплата за продукцию по дог. №267/26, НДС 12%</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>196880000</v>
+        <v>199683000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n">
-        <v>4570000</v>
+        <v>3948000</v>
       </c>
       <c r="D58" s="2" t="n"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Shodlik Qurilish MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>353396700</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000029513757001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №90/26</t>
+          <t>Аренда помещения за август, дог. №12/23</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>192310000</v>
+        <v>195735000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46244</v>
+        <v>46241</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
       <c r="C59" s="2" t="n">
-        <v>6848000</v>
+        <v>24512000</v>
       </c>
       <c r="D59" s="2" t="n"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ilhom Mebel AJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>298850397</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000121172763001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №162/26, QQS bilan</t>
+          <t>Предоплата за материалы по дог. №266/26</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>185462000</v>
+        <v>171223000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
       <c r="C60" s="2" t="n"/>
       <c r="D60" s="2" t="n">
-        <v>4277000</v>
+        <v>16972000</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ziyo Logistik MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>365676312</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>20208000639791779001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №90/26, QQS 12%</t>
+          <t>Оплата за товар по с/ф №3700 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>189739000</v>
+        <v>188195000</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n">
-        <v>50117000</v>
-      </c>
-      <c r="D61" s="2" t="n"/>
+      <c r="C61" s="2" t="n"/>
+      <c r="D61" s="2" t="n">
+        <v>5919000</v>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ilhom Logistik MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>248917833</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000947306345001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2666,232 +2666,237 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №174/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №293 от 10.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>139622000</v>
+        <v>194114000</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="B62" t="n">
         <v>154</v>
       </c>
-      <c r="C62" s="2" t="n"/>
-      <c r="D62" s="2" t="n">
-        <v>17027000</v>
-      </c>
+      <c r="C62" s="2" t="n">
+        <v>7824000</v>
+      </c>
+      <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sarbon Yog' Zavodi XK</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>347697109</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000706950338001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №985 12.08.2026, QQS bilan</t>
+          <t>Оплата за транспортные услуги по договору №208/26</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>156649000</v>
+        <v>186290000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46246</v>
+        <v>46244</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
-      <c r="C63" s="2" t="n"/>
-      <c r="D63" s="2" t="n">
-        <v>7116000</v>
-      </c>
+      <c r="C63" s="2" t="n">
+        <v>38619000</v>
+      </c>
+      <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ziyo Logistik MChJ</t>
+          <t>Denov Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>365676312</t>
+          <t>309642814</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000639791779001</t>
+          <t>20208000113550674001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8808</t>
+          <t>Оплата за сырье по договору №191/26 от 10.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>163765000</v>
+        <v>147671000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46249</v>
+        <v>46244</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>27600000</v>
+        <v>49643000</v>
       </c>
       <c r="D64" s="2" t="n"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-7064)</t>
+          <t>Bekobod Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>16307000208536163417</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-7064 bo'yicha navbatdagi to'lov (08.2026)</t>
+          <t>Предоплата за материалы по договору №216/26</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>136165000</v>
+        <v>98028000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
       <c r="C65" s="2" t="n"/>
       <c r="D65" s="2" t="n">
-        <v>49377000</v>
+        <v>15178000</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>367631266</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000979177978001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Предоплата за товар по дог. №88/26 от 17.08.2026</t>
+          <t>Mahsulot uchun to'lov, shartn. №15/26, QQS 12%</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>185542000</v>
+        <v>113206000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46251</v>
+        <v>46245</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
       <c r="C66" s="2" t="n"/>
       <c r="D66" s="2" t="n">
-        <v>29699000</v>
+        <v>5831000</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Qarshi Poligraf AJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>230915875</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>20208000573226685001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №128/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №6513 от 11.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>215241000</v>
+        <v>119037000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46251</v>
+        <v>46246</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
-      <c r="C67" s="2" t="n"/>
-      <c r="D67" s="2" t="n">
-        <v>22799000</v>
-      </c>
+      <c r="C67" s="2" t="n">
+        <v>7268000</v>
+      </c>
+      <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ziyo Logistik MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>365676312</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000639791779001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2901,211 +2906,206 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №115/26 QQS 12%</t>
+          <t>Оплата за сырье по договору №158/26 от 12.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>238040000</v>
+        <v>111769000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>20763000</v>
+        <v>7969000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Shartnoma №259/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №9234 от 13.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>258803000</v>
+        <v>119738000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
-      <c r="C69" s="2" t="n"/>
-      <c r="D69" s="2" t="n">
-        <v>12089000</v>
-      </c>
+      <c r="C69" s="2" t="n">
+        <v>3833000</v>
+      </c>
+      <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Guliston Meva-Sabzavot AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>326206925</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000152268622001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SHARTNOMA №273/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>СОЦИАЛЬНЫЙ НАЛОГ ЗА ИЮЛЬ 2026 Г.</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>270892000</v>
+        <v>115905000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
-      <c r="C70" s="2" t="n"/>
-      <c r="D70" s="2" t="n">
-        <v>11945000</v>
-      </c>
+      <c r="C70" s="2" t="n">
+        <v>3833000</v>
+      </c>
+      <c r="D70" s="2" t="n"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО С/Ф №6071 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Налог на доходы физических лиц за июль 2026 г.</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>282837000</v>
+        <v>112072000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
       </c>
-      <c r="C71" s="2" t="n"/>
-      <c r="D71" s="2" t="n">
-        <v>6494000</v>
-      </c>
+      <c r="C71" s="2" t="n">
+        <v>12223000</v>
+      </c>
+      <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Denov Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>309642814</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000113550674001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>YETKAZILGAN TOVAR UCHUN TO'LOV H/F №8822</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №63/26</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>289331000</v>
+        <v>99849000</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46251</v>
+        <v>46249</v>
       </c>
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>5109000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>27600000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>310653505</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-7064)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>16307000208536163417</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №1621 17.08.2026, QQS bilan</t>
+          <t>Kredit shartnomasi L-2025-7064 bo'yicha navbatdagi to'lov (08.2026)</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>294440000</v>
+        <v>72249000</v>
       </c>
     </row>
     <row r="73">
@@ -3117,35 +3117,35 @@
       </c>
       <c r="C73" s="2" t="n"/>
       <c r="D73" s="2" t="n">
-        <v>3502000</v>
+        <v>31434000</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Andijon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>265350564</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000730811872001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2740 17.08.2026, QQS bilan</t>
+          <t>Оплата за продукцию по дог. №18/26, НДС 12%</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>297942000</v>
+        <v>103683000</v>
       </c>
     </row>
     <row r="74">
@@ -3155,37 +3155,37 @@
       <c r="B74" t="n">
         <v>166</v>
       </c>
-      <c r="C74" s="2" t="n">
-        <v>3833000</v>
-      </c>
-      <c r="D74" s="2" t="n"/>
+      <c r="C74" s="2" t="n"/>
+      <c r="D74" s="2" t="n">
+        <v>29337000</v>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>Ijtimoiy soliq iyul 2026</t>
+          <t>Оплата по счет-фактуре №8013 за поставленный товар</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>294109000</v>
+        <v>133020000</v>
       </c>
     </row>
     <row r="75">
@@ -3196,36 +3196,36 @@
         <v>167</v>
       </c>
       <c r="C75" s="2" t="n">
-        <v>3833000</v>
+        <v>5734000</v>
       </c>
       <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>НАЛОГ НА ДОХОДЫ ФИЗИЧЕСКИХ ЛИЦ ЗА ИЮЛЬ 2026 Г.</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №292/26</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>290276000</v>
+        <v>127286000</v>
       </c>
     </row>
     <row r="76">
@@ -3236,36 +3236,36 @@
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>7722000</v>
+        <v>10576000</v>
       </c>
       <c r="D76" s="2" t="n"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №290/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №236/26</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>282554000</v>
+        <v>116710000</v>
       </c>
     </row>
     <row r="77">
@@ -3275,23 +3275,23 @@
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>13223000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>60444000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3301,157 +3301,157 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1886 18.08.2026, QQS bilan</t>
+          <t>Предоплата за материалы по договору №67/26</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>295777000</v>
+        <v>56266000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>4043000</v>
+        <v>5009000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>367631266</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000979177978001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №8954 18.08.2026, QQS bilan</t>
+          <t>Предоплата за товар по договору №280/26 от 19.08.2026</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>299820000</v>
+        <v>61275000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
-      <c r="C79" s="2" t="n"/>
-      <c r="D79" s="2" t="n">
-        <v>3881000</v>
-      </c>
+      <c r="C79" s="2" t="n">
+        <v>17582000</v>
+      </c>
+      <c r="D79" s="2" t="n"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ziyo Logistik MChJ</t>
+          <t>Denov Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>365676312</t>
+          <t>309642814</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000639791779001</t>
+          <t>20208000113550674001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1872 от 18.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за сырье по договору №290/26 от 19.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>303701000</v>
+        <v>43693000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>3481000</v>
+        <v>36279000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9646</t>
+          <t>Mahsulot uchun to'lov, shartnoma №39/26, QQS 12%</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>307182000</v>
+        <v>79972000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
       </c>
-      <c r="C81" s="2" t="n"/>
-      <c r="D81" s="2" t="n">
-        <v>7078000</v>
-      </c>
+      <c r="C81" s="2" t="n">
+        <v>14119000</v>
+      </c>
+      <c r="D81" s="2" t="n"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ziyo Logistik MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>365676312</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>20208000639791779001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3461,117 +3461,117 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2393 от 19.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №1070</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>314260000</v>
+        <v>65853000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46253</v>
+        <v>46258</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
       </c>
       <c r="C82" s="2" t="n"/>
       <c r="D82" s="2" t="n">
-        <v>4013000</v>
+        <v>56232000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Andijon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>265350564</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000730811872001</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №65/26, QQS 12%</t>
+          <t>Оплата за продукцию по договору №107/26, НДС 12%</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>318273000</v>
+        <v>122085000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n"/>
       <c r="D83" s="2" t="n">
-        <v>11236000</v>
+        <v>12299000</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>367631266</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000979177978001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SHARTNOMA №54/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за продукцию по договору №11/26, НДС 12%</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>329509000</v>
+        <v>134384000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>11113000</v>
+        <v>9914000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3581,117 +3581,117 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Shartnoma №150/26 bo'yicha oldindan to'lov</t>
+          <t>Shartnoma №45/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>340622000</v>
+        <v>144298000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
-      <c r="C85" s="2" t="n"/>
-      <c r="D85" s="2" t="n">
-        <v>10610000</v>
-      </c>
+      <c r="C85" s="2" t="n">
+        <v>6712000</v>
+      </c>
+      <c r="D85" s="2" t="n"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №7072</t>
+          <t>НДС за июль 2026 г.</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>351232000</v>
+        <v>137586000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
       <c r="C86" s="2" t="n">
-        <v>4200000</v>
+        <v>7152000</v>
       </c>
       <c r="D86" s="2" t="n"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №213/26</t>
+          <t>Оплата за упаковочные материалы, с/ф №1630</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>347032000</v>
+        <v>130434000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
-      <c r="C87" s="2" t="n"/>
-      <c r="D87" s="2" t="n">
-        <v>44477000</v>
-      </c>
+      <c r="C87" s="2" t="n">
+        <v>9713000</v>
+      </c>
+      <c r="D87" s="2" t="n"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>224085958</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000638419757001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -3701,157 +3701,157 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Yetkazilga tovar uchun to'lov h/f №4744</t>
+          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГ. №129/26</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>391509000</v>
+        <v>120721000</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>9960000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>11696000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Guliston Qog'oz AJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>313936393</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000205651328001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8079</t>
+          <t>Предопата за материалы по договору №298/26</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>401469000</v>
+        <v>109025000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>5737000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>36863000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Shartnoma №253/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за транспортные услуги по договору №85/26</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>407206000</v>
+        <v>72162000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>14134000</v>
+        <v>35429000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5624 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГ. №195/26, НДС 12%</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>421340000</v>
+        <v>107591000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n">
-        <v>6767000</v>
-      </c>
+      <c r="C91" s="2" t="n">
+        <v>2468000</v>
+      </c>
+      <c r="D91" s="2" t="n"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000179412176001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3861,357 +3861,357 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6570</t>
+          <t>Оплата за электроэнергию согласно счету</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>428107000</v>
+        <v>105123000</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>6713000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>11262000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Guliston Meva-Sabzavot AJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>326206925</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000152268622001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №14/26, QQS 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №187/26, QQS bilan</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>434820000</v>
+        <v>93861000</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n">
-        <v>6683000</v>
-      </c>
-      <c r="D93" s="2" t="n"/>
+      <c r="C93" s="2" t="n"/>
+      <c r="D93" s="2" t="n">
+        <v>38750000</v>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Nukus Savdo AJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>237734747</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000287266283001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
+          <t>Оплата за продукцию по договору №246/26, НДС 12%</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>428137000</v>
+        <v>132611000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
       </c>
-      <c r="C94" s="2" t="n">
-        <v>10121000</v>
-      </c>
-      <c r="D94" s="2" t="n"/>
+      <c r="C94" s="2" t="n"/>
+      <c r="D94" s="2" t="n">
+        <v>15340000</v>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Andijon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>265350564</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000730811872001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartn. №8/26</t>
+          <t>Оплата за продукцию по дог. №193/26, НДС 12%</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>418016000</v>
+        <v>147951000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
-      <c r="C95" s="2" t="n">
-        <v>11063000</v>
-      </c>
-      <c r="D95" s="2" t="n"/>
+      <c r="C95" s="2" t="n"/>
+      <c r="D95" s="2" t="n">
+        <v>5313000</v>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Durdona Avto Ehtiyot MChJ</t>
+          <t>Andijon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>243368843</t>
+          <t>265350564</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>20208000420339260001</t>
+          <t>20208000730811872001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4111</t>
+          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №130/26 ОТ 26.08.2026</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>406953000</v>
+        <v>153264000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
-      <c r="C96" s="2" t="n">
-        <v>120800000</v>
-      </c>
-      <c r="D96" s="2" t="n"/>
+      <c r="C96" s="2" t="n"/>
+      <c r="D96" s="2" t="n">
+        <v>46400000</v>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Durdona Avto Ehtiyot MChJ</t>
+          <t>Andijon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>243368843</t>
+          <t>265350564</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000420339260001</t>
+          <t>20208000730811872001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5898</t>
+          <t>Предоплата за товар по договору №8/26 от 27.08.2026</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>286153000</v>
+        <v>199664000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>10478000</v>
+        <v>7517000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ziyo Logistik MChJ</t>
+          <t>Andijon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>365676312</t>
+          <t>265350564</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000639791779001</t>
+          <t>20208000730811872001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №4823 от 25.08.2026, в т.ч. НДС 12%</t>
+          <t>ОПЛАТА ЗА ТОВАР ПО СЧЕТ-ФАКТУРЕ №113 ОТ 27.08.2026, В Т.Ч. НДС 12%</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>296631000</v>
+        <v>207181000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
-      <c r="C98" s="2" t="n"/>
-      <c r="D98" s="2" t="n">
-        <v>4772000</v>
-      </c>
+      <c r="C98" s="2" t="n">
+        <v>69228000</v>
+      </c>
+      <c r="D98" s="2" t="n"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>209058766</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000571672220001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №1058 25.08.2026, QQS bilan</t>
+          <t>Оплата за сырье по договору №220/26 от 27.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>301403000</v>
+        <v>137953000</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B99" t="n">
         <v>191</v>
       </c>
-      <c r="C99" s="2" t="n">
-        <v>2468000</v>
-      </c>
-      <c r="D99" s="2" t="n"/>
+      <c r="C99" s="2" t="n"/>
+      <c r="D99" s="2" t="n">
+        <v>10657000</v>
+      </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>367631266</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000025679860001</t>
+          <t>20208000979177978001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Elektr energiyasi uchun to'lov</t>
+          <t>Оплата по счет-фактуре №3241 за поставленный товар</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>298935000</v>
+        <v>148610000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
-      <c r="C100" s="2" t="n">
-        <v>18150000</v>
-      </c>
-      <c r="D100" s="2" t="n"/>
+      <c r="C100" s="2" t="n"/>
+      <c r="D100" s="2" t="n">
+        <v>35286000</v>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Ilhom Logistik MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>248917833</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000947306345001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4221,632 +4221,627 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №96/26, QQS bilan</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9981</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>280785000</v>
+        <v>183896000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>6015000</v>
+        <v>13658000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Andijon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>265350564</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000730811872001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №184</t>
+          <t>Оплата по счет-фактуре №5497 за поставленный товар</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>286800000</v>
+        <v>197554000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
       <c r="C102" s="2" t="n">
-        <v>4664000</v>
+        <v>300000</v>
       </c>
       <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>206971678</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО С/Ф №1646</t>
+          <t>Комиссия за перевод</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>282136000</v>
+        <v>197254000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
-      <c r="C103" s="2" t="n"/>
-      <c r="D103" s="2" t="n">
-        <v>6420000</v>
-      </c>
+      <c r="C103" s="2" t="n">
+        <v>7145000</v>
+      </c>
+      <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Sarbon Yog' Zavodi XK</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>347697109</t>
+          <t>209058766</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>20208000706950338001</t>
+          <t>20208000571672220001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4803 за поставленный товар</t>
+          <t>Предоплата за материалы по договору №6/26</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>288556000</v>
+        <v>190109000</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B104" t="n">
         <v>196</v>
       </c>
       <c r="C104" s="2" t="n">
-        <v>8928000</v>
+        <v>13287000</v>
       </c>
       <c r="D104" s="2" t="n"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Saodat Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>343642020</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000791511261001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА УПАКОВОЧНЫЕ МАТЕРИАЛЫ, С/Ф №5553</t>
+          <t>Оплата за транспортные услуги по договору №140/26</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>279628000</v>
+        <v>176822000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n">
-        <v>14961000</v>
+        <v>27677000</v>
       </c>
       <c r="D105" s="2" t="n"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Durdona Avto Ehtiyot MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>243368843</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000420339260001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTN. №151/26, QQS BILAN</t>
+          <t>Оплата за сырье по договору №175/26 от 31.08.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>264667000</v>
+        <v>149145000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
-      <c r="C106" s="2" t="n">
-        <v>26300000</v>
-      </c>
-      <c r="D106" s="2" t="n"/>
+      <c r="C106" s="2" t="n"/>
+      <c r="D106" s="2" t="n">
+        <v>3333000</v>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №72/26 от 28.08.2026, НДС 12%</t>
+          <t>Оплата за продукцию по договору №175/26, НДС 12%</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>238367000</v>
+        <v>152478000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
       <c r="C107" s="2" t="n"/>
       <c r="D107" s="2" t="n">
-        <v>44460000</v>
+        <v>3491000</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Zarafshon Logistik XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>280377347</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000792872662001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Shartnoma №270/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №3896 от 02.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>282827000</v>
+        <v>155969000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n">
-        <v>300000</v>
+        <v>99105000</v>
       </c>
       <c r="D108" s="2" t="n"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Bekobod Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>BANK XIZMATI UCHUN KOMISSIYA</t>
+          <t>Оплата за сырье по дог. №242/26 от 02.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>282527000</v>
+        <v>56864000</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B109" t="n">
         <v>201</v>
       </c>
       <c r="C109" s="2" t="n">
-        <v>7854000</v>
+        <v>13296000</v>
       </c>
       <c r="D109" s="2" t="n"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Denov Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>309642814</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000113550674001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>XOM ASHYO UCHUN TO'LOV, SHARTNOMA №262/26, QQS BILAN</t>
+          <t>Оплата за товары согласно счет-фактуре №3785</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>274673000</v>
+        <v>43568000</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="B110" t="n">
         <v>202</v>
       </c>
       <c r="C110" s="2" t="n">
-        <v>10123000</v>
+        <v>22663000</v>
       </c>
       <c r="D110" s="2" t="n"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Denov Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>309642814</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000113550674001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №198/26</t>
+          <t>Оплата за товары согласно счет-фактуре №4326</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>264550000</v>
+        <v>20905000</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>46265</v>
+        <v>46272</v>
       </c>
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>119757000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>110833000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Durdona Avto Ehtiyot MChJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>243368843</t>
+          <t>367631266</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000420339260001</t>
+          <t>20208000979177978001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №79/26</t>
+          <t>Предоплата за товар по договору №119/26 от 07.09.2026</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>144793000</v>
+        <v>131738000</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="3" t="n">
-        <v>46266</v>
+        <v>46272</v>
       </c>
       <c r="B112" t="n">
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n"/>
       <c r="D112" s="2" t="n">
-        <v>58023000</v>
+        <v>80729000</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Ziyo Logistik MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>365676312</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>20208000639791779001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Shartnoma №31/26 bo'yicha oldindan to'lov</t>
+          <t>Оплата за товар по счет-фактуре №6237 от 07.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>202816000</v>
+        <v>212467000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46266</v>
+        <v>46272</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>14209000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>28829000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>310653505</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №9134 01.09.2026, QQS bilan</t>
+          <t>Заработная плата за август 2026 г. (перечисление на пластиковые карты)</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>217025000</v>
+        <v>183638000</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="n">
-        <v>46266</v>
+        <v>46272</v>
       </c>
       <c r="B114" t="n">
         <v>206</v>
       </c>
       <c r="C114" s="2" t="n">
-        <v>6782000</v>
+        <v>29495000</v>
       </c>
       <c r="D114" s="2" t="n"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9443</t>
+          <t>Оплата за транспортные услуги по договору №158/26</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>210243000</v>
+        <v>154143000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46266</v>
+        <v>46273</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>146982000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>140983000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Ilhom Mebel AJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>298850397</t>
+          <t>367631266</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000121172763001</t>
+          <t>20208000979177978001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartn. №47/26</t>
+          <t>Оплата за товар по с/ф №7348 от 08.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>63261000</v>
+        <v>295126000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46267</v>
+        <v>46273</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
-      <c r="C116" s="2" t="n">
-        <v>70875000</v>
-      </c>
-      <c r="D116" s="2" t="n"/>
+      <c r="C116" s="2" t="n"/>
+      <c r="D116" s="2" t="n">
+        <v>24884000</v>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Ilhom Logistik MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>248917833</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000947306345001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4856,157 +4851,157 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №9215</t>
+          <t>Оплата за продукцию по договору №213/26, НДС 12%</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>-7614000</v>
+        <v>320010000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n">
-        <v>22721000</v>
-      </c>
+      <c r="C117" s="2" t="n">
+        <v>12549000</v>
+      </c>
+      <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Denov Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>309642814</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000113550674001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Shartnoma №147/26 bo'yicha oldindan to'lov</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №189/26</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>15107000</v>
+        <v>307461000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46268</v>
+        <v>46273</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
       <c r="C118" s="2" t="n">
-        <v>5633000</v>
+        <v>31069000</v>
       </c>
       <c r="D118" s="2" t="n"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №142/26 от 03.09.2026, НДС 12%</t>
+          <t>Предоплата за материалы по договору №71/26</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>9474000</v>
+        <v>276392000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
       <c r="C119" s="2" t="n"/>
       <c r="D119" s="2" t="n">
-        <v>13314000</v>
+        <v>9435000</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №181/26, QQS 12%</t>
+          <t>Предоплата за товар по договору №16/26 от 09.09.2026</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>22788000</v>
+        <v>285827000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n"/>
       <c r="D120" s="2" t="n">
-        <v>7433000</v>
+        <v>5650000</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -5016,152 +5011,157 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Shartnoma №192/26 bo'yicha oldindan to'lov</t>
+          <t>Tovar uchun to'lov, h/f №2674 09.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>30221000</v>
+        <v>291477000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>28829000</v>
+        <v>4049000</v>
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Navbahor Bank ATB</t>
+          <t>Shodlik Qurilish MChJ</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>353396700</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000029513757001</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ish haqi, reestr №4646</t>
+          <t>Арендная плата за сентябрь 2026 г. по договору №12/23</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1392000</v>
+        <v>287428000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
-      <c r="C122" s="2" t="n"/>
-      <c r="D122" s="2" t="n">
-        <v>75554000</v>
-      </c>
+      <c r="C122" s="2" t="n">
+        <v>11096000</v>
+      </c>
+      <c r="D122" s="2" t="n"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Denov Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>309642814</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000113550674001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №25/26, НДС 12%</t>
+          <t>Оплата за сырье по договору №3/26 от 09.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>76946000</v>
+        <v>276332000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46272</v>
+        <v>46275</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n"/>
-      <c r="D123" s="2" t="n">
-        <v>16682000</v>
-      </c>
+      <c r="C123" s="2" t="n">
+        <v>17191000</v>
+      </c>
+      <c r="D123" s="2" t="n"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Denov Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>309642814</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000113550674001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Shartnoma №286/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за материалы по договору №210/26</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>93628000</v>
+        <v>259141000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
       <c r="C124" s="2" t="n"/>
       <c r="D124" s="2" t="n">
-        <v>15931000</v>
+        <v>5197000</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5171,277 +5171,272 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №136/26 от 07.09.2026</t>
+          <t>Оплата за продукцию по дог. №16/26, НДС 12%</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>109559000</v>
+        <v>264338000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46272</v>
+        <v>46280</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
-      <c r="C125" s="2" t="n"/>
-      <c r="D125" s="2" t="n">
-        <v>6510000</v>
-      </c>
+      <c r="C125" s="2" t="n">
+        <v>27600000</v>
+      </c>
+      <c r="D125" s="2" t="n"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>222000978</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2025-7064)</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>16307000208536163417</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8140</t>
+          <t>Kredit shartnomasi L-2025-7064 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>116069000</v>
+        <v>236738000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46272</v>
+        <v>46281</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>4049000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>7819000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Gulshan Qurilish MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>372974759</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000631506069001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Аренда помещения за сентябрь, дог. №53/25</t>
+          <t>Mahsulot uchun to'lov, shartn. №14/26, QQS 12%</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>112020000</v>
+        <v>244557000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46272</v>
+        <v>46281</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
       <c r="C127" s="2" t="n">
-        <v>5380000</v>
+        <v>3931000</v>
       </c>
       <c r="D127" s="2" t="n"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Ilhom Mebel AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>298850397</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000121172763001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №183/26</t>
+          <t>УПЛАТА СОЦИАЛЬНОГО НАЛОГА ЗА АВГУСТ</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>106640000</v>
+        <v>240626000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46272</v>
+        <v>46281</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n">
-        <v>11311000</v>
+        <v>3931000</v>
       </c>
       <c r="D128" s="2" t="n"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>MATERIALLAR UCHUN OLDINDAN TO'LOV, SHARTNOMA №117/26</t>
+          <t>Налог на доходы физических лиц за август 2026 г.</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>95329000</v>
+        <v>236695000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46272</v>
+        <v>46282</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n">
-        <v>14741000</v>
-      </c>
-      <c r="D129" s="2" t="n"/>
+      <c r="C129" s="2" t="n"/>
+      <c r="D129" s="2" t="n">
+        <v>7885000</v>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Andijon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>265350564</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000730811872001</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartn. №237/26,QQS bilan</t>
+          <t>Оплата за продукцию по дог. №254/26, НДС 12%</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>80588000</v>
+        <v>244580000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46273</v>
+        <v>46283</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
       <c r="C130" s="2" t="n"/>
       <c r="D130" s="2" t="n">
-        <v>61859000</v>
+        <v>7061000</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>224085958</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000638419757001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №204/26, НДС 12%</t>
+          <t>Оплата за товар по счет-фактуре №2026 от 18.09.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>142447000</v>
+        <v>251641000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46273</v>
+        <v>46283</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>12736000</v>
+        <v>4265000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -5451,397 +5446,397 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3751 08.09.2026, QQS bilan</t>
+          <t>Оплата по счет-фактуре №17 за поставленный товар</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>155183000</v>
+        <v>255906000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46273</v>
+        <v>46286</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n">
-        <v>14183000</v>
-      </c>
-      <c r="D132" s="2" t="n"/>
+      <c r="C132" s="2" t="n"/>
+      <c r="D132" s="2" t="n">
+        <v>7209000</v>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Durdona Avto Ehtiyot MChJ</t>
+          <t>Mehnat Un Mahsulotlari XK</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>243368843</t>
+          <t>367631266</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000420339260001</t>
+          <t>20208000979177978001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №5949</t>
+          <t>Оплата по счет-фактуре №2187 за поставленный товар</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>141000000</v>
+        <v>263115000</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="3" t="n">
-        <v>46274</v>
+        <v>46286</v>
       </c>
       <c r="B133" t="n">
         <v>225</v>
       </c>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n">
-        <v>8300000</v>
-      </c>
+      <c r="C133" s="2" t="n">
+        <v>6719000</v>
+      </c>
+      <c r="D133" s="2" t="n"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Qarshi Poligraf AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>230915875</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000573226685001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8607 от 09.09.2026, в т.ч. НДС 12%</t>
+          <t>QQS avgust 2026 uchun</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>149300000</v>
+        <v>256396000</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="3" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n"/>
-      <c r="D134" s="2" t="n">
-        <v>19395000</v>
-      </c>
+      <c r="C134" s="2" t="n">
+        <v>25920000</v>
+      </c>
+      <c r="D134" s="2" t="n"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Toshkent Farm Savdo MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>209058766</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000571672220001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>SHARTNOMA №92/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Предоплата за материалы по договору №72/26</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>168695000</v>
+        <v>230476000</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="3" t="n">
-        <v>46276</v>
+        <v>46286</v>
       </c>
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n"/>
-      <c r="D135" s="2" t="n">
-        <v>9249000</v>
-      </c>
+      <c r="C135" s="2" t="n">
+        <v>26725000</v>
+      </c>
+      <c r="D135" s="2" t="n"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>SHARTNOMA №95/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за товары согласно счет-фактуре №1345</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>177944000</v>
+        <v>203751000</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="3" t="n">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="B136" t="n">
         <v>228</v>
       </c>
-      <c r="C136" s="2" t="n"/>
-      <c r="D136" s="2" t="n">
-        <v>43953000</v>
-      </c>
+      <c r="C136" s="2" t="n">
+        <v>37716000</v>
+      </c>
+      <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Denov Farm Savdo AJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>309642814</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000113550674001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>SHARTNOMA №293/26 BO'YICHA OLDINDAN TO'LOV</t>
+          <t>Оплата за сырье по договору №161/26 от 21.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>221897000</v>
+        <v>166035000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46279</v>
+        <v>46287</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n"/>
       <c r="D137" s="2" t="n">
-        <v>17617000</v>
+        <v>4656000</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Shartnoma №254/26 bo'yicha oldindan to'lov</t>
+          <t>Предоплата за товар по договору №118/26 от 22.09.2026</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>239514000</v>
+        <v>170691000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46279</v>
+        <v>46288</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n"/>
       <c r="D138" s="2" t="n">
-        <v>16911000</v>
+        <v>24992000</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Ziyo Logistik MChJ</t>
+          <t>Andijon Un Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>365676312</t>
+          <t>265350564</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000639791779001</t>
+          <t>20208000730811872001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №9/26, НДС 12%</t>
+          <t>Оплата по счет-фактуре №7182 за поставленный товар</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>256425000</v>
+        <v>195683000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46279</v>
+        <v>46288</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>13831000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>2531000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Termiz Metall Servis MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>310653505</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000487308118001</t>
+          <t>20208000179412176001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №9380 14.09.2026, QQS bilan</t>
+          <t>ELEKTR ENERGIYASI UCHUN TO'LOV</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>270256000</v>
+        <v>193152000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46279</v>
+        <v>46288</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n">
-        <v>6935000</v>
+        <v>20403000</v>
       </c>
       <c r="D140" s="2" t="n"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Durdona Avto Ehtiyot MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>243368843</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000420339260001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6193</t>
+          <t>Оплата за упаковочные материалы, с/ф №2070</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>263321000</v>
+        <v>172749000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46279</v>
+        <v>46289</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n">
-        <v>14036000</v>
-      </c>
-      <c r="D141" s="2" t="n"/>
+      <c r="C141" s="2" t="n"/>
+      <c r="D141" s="2" t="n">
+        <v>13978000</v>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ilhom Logistik MChJ</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>248917833</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000947306345001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -5851,1026 +5846,351 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по дог. №43/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №295/26, QQS 12%</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>249285000</v>
+        <v>186727000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46279</v>
+        <v>46289</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n">
-        <v>46581000</v>
+        <v>70410000</v>
       </c>
       <c r="D142" s="2" t="n"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №191/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №233/26</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>202704000</v>
+        <v>116317000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46280</v>
+        <v>46290</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
       <c r="C143" s="2" t="n">
-        <v>27600000</v>
+        <v>12294000</v>
       </c>
       <c r="D143" s="2" t="n"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2025-7064)</t>
+          <t>Bekobod Savdo MChJ</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>16307000208536163417</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2025-7064 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата за сырье по договору №263/26 от 25.09.2026, НДС 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>175104000</v>
+        <v>104023000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46281</v>
+        <v>46293</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
-      <c r="C144" s="2" t="n">
-        <v>3931000</v>
-      </c>
-      <c r="D144" s="2" t="n"/>
+      <c r="C144" s="2" t="n"/>
+      <c r="D144" s="2" t="n">
+        <v>39575000</v>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Avgust oyi uchun ijtimoiy soliq</t>
+          <t>Shartnoma №21/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>171173000</v>
+        <v>143598000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46281</v>
+        <v>46294</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n">
-        <v>3931000</v>
-      </c>
-      <c r="D145" s="2" t="n"/>
+      <c r="C145" s="2" t="n"/>
+      <c r="D145" s="2" t="n">
+        <v>7340000</v>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Navoiy Sut Mahsulotlari MChJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>369710937</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000695033896001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>JShDS avgust oyi uchun</t>
+          <t>Оплата по счет-фактуре №6364 за поставленный товар</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>167242000</v>
+        <v>150938000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46281</v>
+        <v>46294</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
       <c r="C146" s="2" t="n">
-        <v>7744000</v>
+        <v>12211000</v>
       </c>
       <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Tovarlar uchun to'lov h/f №3474</t>
+          <t>Предоплата за материалы по договору №9/26</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>159498000</v>
+        <v>138727000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46281</v>
+        <v>46294</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n">
-        <v>8418000</v>
+        <v>28220000</v>
       </c>
       <c r="D147" s="2" t="n"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Zafar Trans Servis MChJ</t>
+          <t>Bekobod Savdo MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>206971678</t>
+          <t>291587595</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000726769743001</t>
+          <t>20208000322668547001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Materiallar uchun oldindan to'lov, shartnoma №235/26</t>
+          <t>Оплата за товары согласно счет-фактуре №9904</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>151080000</v>
+        <v>110507000</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="3" t="n">
-        <v>46282</v>
+        <v>46295</v>
       </c>
       <c r="B148" t="n">
         <v>240</v>
       </c>
       <c r="C148" s="2" t="n"/>
       <c r="D148" s="2" t="n">
-        <v>23065000</v>
+        <v>50593000</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Omad Mebel XK</t>
+          <t>Navoiy Metall Servis MChJ</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>222000978</t>
+          <t>200097874</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>20208000465877607001</t>
+          <t>20208000587760746001</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2786</t>
+          <t>Предоплата за товар по договору №19/26 от 30.09.2026</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>174145000</v>
+        <v>161100000</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="3" t="n">
-        <v>46286</v>
+        <v>46295</v>
       </c>
       <c r="B149" t="n">
         <v>241</v>
       </c>
-      <c r="C149" s="2" t="n"/>
-      <c r="D149" s="2" t="n">
-        <v>13267000</v>
-      </c>
+      <c r="C149" s="2" t="n">
+        <v>300000</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Olmaliq Dori-Darmon MChJ</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>224085958</t>
+          <t>Navbahor Bank ATB</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>20208000638419757001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4505 21.09.2026, QQS bilan</t>
+          <t>Hisob-kassa xizmati uchun haq</t>
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>187412000</v>
+        <v>160800000</v>
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B150" t="n">
-        <v>242</v>
-      </c>
-      <c r="C150" s="2" t="n"/>
-      <c r="D150" s="2" t="n">
-        <v>10731000</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Ziyo Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>365676312</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>20208000639791779001</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №9004</t>
-        </is>
-      </c>
-      <c r="J150" s="2" t="n">
-        <v>198143000</v>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Итого обороты:</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="n">
+        <v>1658998000</v>
+      </c>
+      <c r="D150" s="4" t="n">
+        <v>1671998000</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B151" t="n">
-        <v>243</v>
-      </c>
-      <c r="C151" s="2" t="n"/>
-      <c r="D151" s="2" t="n">
-        <v>7622000</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Omad Mebel XK</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>222000978</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>20208000465877607001</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I151" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3622 21.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J151" s="2" t="n">
-        <v>205765000</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B152" t="n">
-        <v>244</v>
-      </c>
-      <c r="C152" s="2" t="n">
-        <v>6804000</v>
-      </c>
-      <c r="D152" s="2" t="n"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>201122905</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>23402000300100001010</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>00014</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>УПЛАТА НАЛОГА НА ДОБАВЛЕННУЮ СТОИМОСТЬ ЗА АВГУСТ</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="n">
-        <v>198961000</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B153" t="n">
-        <v>245</v>
-      </c>
-      <c r="C153" s="2" t="n">
-        <v>10733000</v>
-      </c>
-      <c r="D153" s="2" t="n"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Ilhom Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>248917833</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>20208000947306345001</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №2963</t>
-        </is>
-      </c>
-      <c r="J153" s="2" t="n">
-        <v>188228000</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="3" t="n">
-        <v>46286</v>
-      </c>
-      <c r="B154" t="n">
-        <v>246</v>
-      </c>
-      <c r="C154" s="2" t="n">
-        <v>14827000</v>
-      </c>
-      <c r="D154" s="2" t="n"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Zafar Trans Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>206971678</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>20208000726769743001</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>01153</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №270/26</t>
-        </is>
-      </c>
-      <c r="J154" s="2" t="n">
-        <v>173401000</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="n">
-        <v>46287</v>
-      </c>
-      <c r="B155" t="n">
-        <v>247</v>
-      </c>
-      <c r="C155" s="2" t="n">
-        <v>32629000</v>
-      </c>
-      <c r="D155" s="2" t="n"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Ilhom Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>248917833</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>20208000947306345001</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Tovarlar uchun to'lov h/f №3986</t>
-        </is>
-      </c>
-      <c r="J155" s="2" t="n">
-        <v>140772000</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B156" t="n">
-        <v>248</v>
-      </c>
-      <c r="C156" s="2" t="n"/>
-      <c r="D156" s="2" t="n">
-        <v>7834000</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Termiz Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>310653505</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>20208000487308118001</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, h/f №2225 24.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J156" s="2" t="n">
-        <v>148606000</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B157" t="n">
-        <v>249</v>
-      </c>
-      <c r="C157" s="2" t="n"/>
-      <c r="D157" s="2" t="n">
-        <v>6926000</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Zarafshon Logistik XK</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>280377347</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>20208000792872662001</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>00987</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>Mahsulot uchun to'lov, shartnoma №197/26, QQS 12%</t>
-        </is>
-      </c>
-      <c r="J157" s="2" t="n">
-        <v>155532000</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="3" t="n">
-        <v>46289</v>
-      </c>
-      <c r="B158" t="n">
-        <v>250</v>
-      </c>
-      <c r="C158" s="2" t="n">
-        <v>2531000</v>
-      </c>
-      <c r="D158" s="2" t="n"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>200933985</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>20208000025679860001</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>Elektr energiyasi uchun to'lov</t>
-        </is>
-      </c>
-      <c r="J158" s="2" t="n">
-        <v>153001000</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="3" t="n">
-        <v>46290</v>
-      </c>
-      <c r="B159" t="n">
-        <v>251</v>
-      </c>
-      <c r="C159" s="2" t="n">
-        <v>29538000</v>
-      </c>
-      <c r="D159" s="2" t="n"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Ilhom Mebel AJ</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>298850397</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>20208000121172763001</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>00962</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №122/26</t>
-        </is>
-      </c>
-      <c r="J159" s="2" t="n">
-        <v>123463000</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B160" t="n">
-        <v>252</v>
-      </c>
-      <c r="C160" s="2" t="n"/>
-      <c r="D160" s="2" t="n">
-        <v>23544000</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Omad Mebel XK</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>222000978</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>20208000465877607001</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>Shartnoma №275/26 bo'yicha oldindan to'lov</t>
-        </is>
-      </c>
-      <c r="J160" s="2" t="n">
-        <v>147007000</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B161" t="n">
-        <v>253</v>
-      </c>
-      <c r="C161" s="2" t="n"/>
-      <c r="D161" s="2" t="n">
-        <v>14248000</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Omad Mebel XK</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>222000978</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>20208000465877607001</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr">
-        <is>
-          <t>Tovar uchun to'lov, hisob-faktura №3035 28.09.2026, QQS bilan</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="n">
-        <v>161255000</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B162" t="n">
-        <v>254</v>
-      </c>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n">
-        <v>11387000</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Omad Mebel XK</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>222000978</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>20208000465877607001</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>01089</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr">
-        <is>
-          <t>Оплата за товар по с/ф №5014 от 28.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J162" s="2" t="n">
-        <v>172642000</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B163" t="n">
-        <v>255</v>
-      </c>
-      <c r="C163" s="2" t="n">
-        <v>5611000</v>
-      </c>
-      <c r="D163" s="2" t="n"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Ilhom Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>248917833</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>20208000947306345001</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №49/26</t>
-        </is>
-      </c>
-      <c r="J163" s="2" t="n">
-        <v>167031000</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="3" t="n">
-        <v>46293</v>
-      </c>
-      <c r="B164" t="n">
-        <v>256</v>
-      </c>
-      <c r="C164" s="2" t="n">
-        <v>20079000</v>
-      </c>
-      <c r="D164" s="2" t="n"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Ilhom Logistik MChJ</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>248917833</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>20208000947306345001</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №46/26</t>
-        </is>
-      </c>
-      <c r="J164" s="2" t="n">
-        <v>146952000</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B165" t="n">
-        <v>257</v>
-      </c>
-      <c r="C165" s="2" t="n"/>
-      <c r="D165" s="2" t="n">
-        <v>14148000</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Termiz Metall Servis MChJ</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>310653505</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>20208000487308118001</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>01204</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>Оплата за товар по счет-фактуре №7324 от 30.09.2026, в т.ч. НДС 12%</t>
-        </is>
-      </c>
-      <c r="J165" s="2" t="n">
-        <v>161100000</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="3" t="n">
-        <v>46295</v>
-      </c>
-      <c r="B166" t="n">
-        <v>258</v>
-      </c>
-      <c r="C166" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D166" s="2" t="n"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Navbahor Bank ATB</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>45994000900000001001</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>01121</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="n">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Исходящий остаток на 30.09.2026:</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="n">
         <v>160800000</v>
       </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Итого обороты:</t>
-        </is>
-      </c>
-      <c r="C167" s="4" t="n">
-        <v>1667150000</v>
-      </c>
-      <c r="D167" s="4" t="n">
-        <v>1680150000</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Исходящий остаток на 30.09.2026:</t>
-        </is>
-      </c>
-      <c r="C168" s="4" t="n">
-        <v>160800000</v>
-      </c>
-      <c r="D168" s="4" t="n"/>
+      <c r="D151" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
